--- a/data/forms.xlsx
+++ b/data/forms.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="82">
   <si>
     <t>Отметка времени</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Мужской</t>
   </si>
   <si>
-    <t>63 - 70</t>
+    <t>63-70</t>
   </si>
   <si>
     <t>Универсальный</t>
@@ -94,7 +94,7 @@
     <t>Женский</t>
   </si>
   <si>
-    <t>75+</t>
+    <t>75-</t>
   </si>
   <si>
     <t>Атакующий</t>
@@ -121,9 +121,6 @@
     <t>Нервничаешь</t>
   </si>
   <si>
-    <t xml:space="preserve">до 45 </t>
-  </si>
-  <si>
     <t>Контратакующий</t>
   </si>
   <si>
@@ -193,9 +190,6 @@
     <t>Выносливость</t>
   </si>
   <si>
-    <t>50 - 56</t>
-  </si>
-  <si>
     <t xml:space="preserve">Агапов Илья </t>
   </si>
   <si>
@@ -257,9 +251,6 @@
   </si>
   <si>
     <t>Витомсков Владимир</t>
-  </si>
-  <si>
-    <t>63-70</t>
   </si>
   <si>
     <t xml:space="preserve">Бори Кибардин </t>
@@ -308,7 +299,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -329,6 +320,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -788,17 +782,17 @@
       <c r="D4" s="6">
         <v>17.0</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7">
+        <v>-45.0</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>20</v>
@@ -813,7 +807,7 @@
         <v>22</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N4" s="6" t="s">
         <v>35</v>
@@ -824,7 +818,7 @@
         <v>46126.771569212964</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>26</v>
@@ -833,16 +827,16 @@
         <v>15.0</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>29</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>31</v>
@@ -857,7 +851,7 @@
         <v>22</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N5" s="6" t="s">
         <v>24</v>
@@ -868,7 +862,7 @@
         <v>46126.773889421296</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>15</v>
@@ -877,19 +871,19 @@
         <v>15.0</v>
       </c>
       <c r="E6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>32</v>
@@ -912,7 +906,7 @@
         <v>46126.77392078703</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>15</v>
@@ -921,7 +915,7 @@
         <v>15.0</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>17</v>
@@ -930,7 +924,7 @@
         <v>29</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>20</v>
@@ -945,7 +939,7 @@
         <v>22</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N7" s="6" t="s">
         <v>35</v>
@@ -956,7 +950,7 @@
         <v>46126.774411817125</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>15</v>
@@ -974,7 +968,7 @@
         <v>18</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>20</v>
@@ -992,7 +986,7 @@
         <v>23</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
@@ -1000,7 +994,7 @@
         <v>46126.7752221875</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>15</v>
@@ -1009,7 +1003,7 @@
         <v>15.0</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>17</v>
@@ -1018,7 +1012,7 @@
         <v>18</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>20</v>
@@ -1030,10 +1024,10 @@
         <v>33</v>
       </c>
       <c r="L9" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="N9" s="6" t="s">
         <v>24</v>
@@ -1050,7 +1044,7 @@
         <v>16.0</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>17</v>
@@ -1059,7 +1053,7 @@
         <v>18</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>20</v>
@@ -1085,7 +1079,7 @@
         <v>46126.77664003472</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>15</v>
@@ -1094,7 +1088,7 @@
         <v>16.0</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>28</v>
@@ -1103,10 +1097,10 @@
         <v>18</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>20</v>
@@ -1118,10 +1112,10 @@
         <v>22</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
@@ -1135,16 +1129,16 @@
         <v>17.0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>17</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>20</v>
@@ -1153,13 +1147,13 @@
         <v>32</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N12" s="6" t="s">
         <v>24</v>
@@ -1170,7 +1164,7 @@
         <v>46126.77854337963</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>15</v>
@@ -1179,7 +1173,7 @@
         <v>17.0</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>17</v>
@@ -1188,7 +1182,7 @@
         <v>29</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>20</v>
@@ -1200,7 +1194,7 @@
         <v>21</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>23</v>
@@ -1214,7 +1208,7 @@
         <v>46126.784498368055</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>26</v>
@@ -1223,7 +1217,7 @@
         <v>17.0</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>17</v>
@@ -1232,7 +1226,7 @@
         <v>29</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>31</v>
@@ -1247,7 +1241,7 @@
         <v>22</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="N14" s="6" t="s">
         <v>24</v>
@@ -1258,7 +1252,7 @@
         <v>46126.78794581018</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>15</v>
@@ -1267,7 +1261,7 @@
         <v>21.0</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>17</v>
@@ -1276,7 +1270,7 @@
         <v>29</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>20</v>
@@ -1288,10 +1282,10 @@
         <v>21</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N15" s="6" t="s">
         <v>24</v>
@@ -1307,17 +1301,17 @@
       <c r="D16" s="6">
         <v>17.0</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="7">
         <v>62.0</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>29</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>31</v>
@@ -1329,10 +1323,10 @@
         <v>21</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N16" s="6" t="s">
         <v>24</v>
@@ -1343,7 +1337,7 @@
         <v>46126.79991821759</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>26</v>
@@ -1352,19 +1346,19 @@
         <v>25.0</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F17" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G17" s="6" t="s">
-        <v>38</v>
-      </c>
       <c r="H17" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>20</v>
@@ -1373,13 +1367,13 @@
         <v>21</v>
       </c>
       <c r="L17" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="M17" s="6" t="s">
-        <v>59</v>
-      </c>
       <c r="N17" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
@@ -1387,7 +1381,7 @@
         <v>46126.88649247686</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>26</v>
@@ -1396,7 +1390,7 @@
         <v>25.0</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>28</v>
@@ -1405,7 +1399,7 @@
         <v>18</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>31</v>
@@ -1417,10 +1411,10 @@
         <v>21</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N18" s="6" t="s">
         <v>35</v>
@@ -1431,7 +1425,7 @@
         <v>46127.403489641205</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>15</v>
@@ -1440,16 +1434,16 @@
         <v>23.0</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>29</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>20</v>
@@ -1464,7 +1458,7 @@
         <v>22</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N19" s="6" t="s">
         <v>35</v>
